--- a/00_团队成员任务记录表.xlsx
+++ b/00_团队成员任务记录表.xlsx
@@ -1,45 +1,59 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\Training\property-management\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A554FC32-B28A-470D-89A0-091D8B8BB4F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="4020" yWindow="2390" windowWidth="19200" windowHeight="10060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t>7月3号</t>
+  </si>
+  <si>
+    <t>7月4号</t>
+  </si>
+  <si>
+    <t>7月5号</t>
+  </si>
+  <si>
+    <t>7月6号</t>
+  </si>
+  <si>
+    <t>7月7号</t>
+  </si>
+  <si>
+    <t>胡林康</t>
+  </si>
+  <si>
+    <t>高攀</t>
+  </si>
+  <si>
+    <t>李军霖</t>
+  </si>
+  <si>
+    <t>吴兴强</t>
+  </si>
+  <si>
+    <t>向乾坤</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -66,7 +80,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -92,44 +106,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -159,12 +173,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -203,158 +217,256 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1">
-        <v>111</v>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/00_团队成员任务记录表.xlsx
+++ b/00_团队成员任务记录表.xlsx
@@ -1,20 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
-  </bookViews>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
@@ -22,11 +14,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -79,44 +71,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -146,12 +138,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -190,150 +182,210 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/00_团队成员任务记录表.xlsx
+++ b/00_团队成员任务记录表.xlsx
@@ -4,10 +4,42 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId3"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+  <si>
+    <t>7月4号</t>
+  </si>
+  <si>
+    <t>7月5号</t>
+  </si>
+  <si>
+    <t>7月6号</t>
+  </si>
+  <si>
+    <t>7月7号</t>
+  </si>
+  <si>
+    <t>胡林康</t>
+  </si>
+  <si>
+    <t>高攀</t>
+  </si>
+  <si>
+    <t>李军霖</t>
+  </si>
+  <si>
+    <t>吴兴强</t>
+  </si>
+  <si>
+    <t>向乾坤</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -382,9 +414,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/00_团队成员任务记录表.xlsx
+++ b/00_团队成员任务记录表.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>7月4号</t>
   </si>
@@ -38,6 +38,18 @@
   </si>
   <si>
     <t>向乾坤</t>
+  </si>
+  <si>
+    <t>前端框架搭建，页面初始化</t>
+  </si>
+  <si>
+    <t>基础页面搭建</t>
+  </si>
+  <si>
+    <t>前后端接口匹配，功能细节实现</t>
+  </si>
+  <si>
+    <t>页面细节调整</t>
   </si>
 </sst>
 </file>
@@ -417,7 +429,12 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+    <col min="1" max="1" width="13.571428571428571" customWidth="1"/>
+    <col min="2" max="2" width="20.857142857142858" customWidth="1"/>
+    <col min="3" max="3" width="18.857142857142858" customWidth="1"/>
+    <col min="4" max="4" width="34.285714285714285" customWidth="1"/>
+    <col min="5" max="5" width="25.857142857142858" customWidth="1"/>
+    <col min="6" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.25">
@@ -457,9 +474,21 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/00_团队成员任务记录表.xlsx
+++ b/00_团队成员任务记录表.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>7月4号</t>
   </si>
@@ -35,6 +35,15 @@
   </si>
   <si>
     <t>吴兴强</t>
+  </si>
+  <si>
+    <t>部分前端代码修改，api连通测试</t>
+  </si>
+  <si>
+    <t>投诉管理，所有管理增删改查</t>
+  </si>
+  <si>
+    <t>房屋界面按钮优化，状态栏完善，用户登录</t>
   </si>
   <si>
     <t>向乾坤</t>
@@ -417,7 +426,11 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+    <col min="1" max="1" width="13.571428571428571" customWidth="1"/>
+    <col min="2" max="2" width="31.428571428571427" customWidth="1"/>
+    <col min="3" max="3" width="34.57142857142857" customWidth="1"/>
+    <col min="4" max="4" width="48.42857142857143" customWidth="1"/>
+    <col min="5" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.25">
@@ -452,14 +465,23 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/00_团队成员任务记录表.xlsx
+++ b/00_团队成员任务记录表.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>7月4号</t>
   </si>
@@ -29,6 +29,18 @@
   </si>
   <si>
     <t>高攀</t>
+  </si>
+  <si>
+    <t>数据库设计与实体类创建</t>
+  </si>
+  <si>
+    <t>Building和Community两个数据表得后端代码编写</t>
+  </si>
+  <si>
+    <t>repair和repair_order两个数据表的后端代码编写</t>
+  </si>
+  <si>
+    <t>inspection和inspection_record两个数据表的后端代码编写</t>
   </si>
   <si>
     <t>李军霖</t>
@@ -459,36 +471,48 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/00_团队成员任务记录表.xlsx
+++ b/00_团队成员任务记录表.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>7月4号</t>
   </si>
@@ -44,6 +44,18 @@
   </si>
   <si>
     <t>李军霖</t>
+  </si>
+  <si>
+    <t>项目初始化、RBAC权限模块、登录注册、房屋管理、接口统一、Token管理、跨域配置、数据库设计</t>
+  </si>
+  <si>
+    <t>报修投诉模块、财务模块开发、收费规则优化、主键算法优化</t>
+  </si>
+  <si>
+    <t>业务编号统一自动生成（投诉、报修、账单、缴费、缴费记录）</t>
+  </si>
+  <si>
+    <t>删除冗余代码、项目整理、功能联调及代码合并</t>
   </si>
   <si>
     <t>吴兴强</t>
@@ -442,10 +454,10 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="13.571428571428571" customWidth="1"/>
-    <col min="2" max="2" width="20.857142857142858" customWidth="1"/>
-    <col min="3" max="3" width="18.857142857142858" customWidth="1"/>
-    <col min="4" max="4" width="34.285714285714285" customWidth="1"/>
-    <col min="5" max="5" width="25.857142857142858" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="20.142857142857142" customWidth="1"/>
+    <col min="4" max="4" width="23.857142857142858" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
@@ -488,31 +500,43 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/00_团队成员任务记录表.xlsx
+++ b/00_团队成员任务记录表.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>7月4号</t>
   </si>
@@ -61,13 +61,25 @@
     <t>吴兴强</t>
   </si>
   <si>
+    <t>完善报修前端代码，并测试api连通</t>
+  </si>
+  <si>
+    <t>投诉管理，所有模块的删除和新增功能</t>
+  </si>
+  <si>
+    <t>用户界面和所有界面的完善</t>
+  </si>
+  <si>
+    <t>细节修改和界面优化</t>
+  </si>
+  <si>
     <t>向乾坤</t>
   </si>
   <si>
     <t>前端框架搭建，页面初始化</t>
   </si>
   <si>
-    <t>基础页面搭建</t>
+    <t>基础页面搭建，用户管理，角色管理实现</t>
   </si>
   <si>
     <t>前后端接口匹配，功能细节实现</t>
@@ -454,10 +466,10 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="13.571428571428571" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="20.142857142857142" customWidth="1"/>
-    <col min="4" max="4" width="23.857142857142858" customWidth="1"/>
-    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="2" max="2" width="48" customWidth="1"/>
+    <col min="3" max="3" width="51.714285714285715" customWidth="1"/>
+    <col min="4" max="4" width="33.285714285714285" customWidth="1"/>
+    <col min="5" max="5" width="27.571428571428573" customWidth="1"/>
     <col min="6" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
@@ -517,26 +529,38 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/00_团队成员任务记录表.xlsx
+++ b/00_团队成员任务记录表.xlsx
@@ -64,10 +64,10 @@
     <t>完善报修前端代码，并测试api连通</t>
   </si>
   <si>
-    <t>投诉管理，所有模块的删除和新增功能</t>
-  </si>
-  <si>
-    <t>用户界面和所有界面的完善</t>
+    <t>投诉管理，报修管理，实现以及所有模块的删除和新增功能</t>
+  </si>
+  <si>
+    <t>用户界面实现和所有界面的完善</t>
   </si>
   <si>
     <t>细节修改和界面优化</t>
@@ -79,7 +79,7 @@
     <t>前端框架搭建，页面初始化</t>
   </si>
   <si>
-    <t>基础页面搭建，用户管理，角色管理实现</t>
+    <t>基础页面搭建，用户管理，角色管理，登录注册，缴费管理，账单管理实现</t>
   </si>
   <si>
     <t>前后端接口匹配，功能细节实现</t>

--- a/00_团队成员任务记录表.xlsx
+++ b/00_团队成员任务记录表.xlsx
@@ -34,7 +34,7 @@
     <t>数据库设计与实体类创建</t>
   </si>
   <si>
-    <t>Building和Community两个数据表得后端代码编写</t>
+    <t>Building和Community两个数据表的后端代码编写</t>
   </si>
   <si>
     <t>repair和repair_order两个数据表的后端代码编写</t>
@@ -466,8 +466,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="13.571428571428571" customWidth="1"/>
-    <col min="2" max="2" width="48" customWidth="1"/>
-    <col min="3" max="3" width="51.714285714285715" customWidth="1"/>
+    <col min="2" max="3" width="42.142857142857146" customWidth="1"/>
     <col min="4" max="4" width="33.285714285714285" customWidth="1"/>
     <col min="5" max="5" width="27.571428571428573" customWidth="1"/>
     <col min="6" max="24" width="13.571428571428571" customWidth="1"/>

--- a/00_团队成员任务记录表.xlsx
+++ b/00_团队成员任务记录表.xlsx
@@ -55,7 +55,7 @@
     <t>业务编号统一自动生成（投诉、报修、账单、缴费、缴费记录）</t>
   </si>
   <si>
-    <t>删除冗余代码、项目整理、功能联调及代码合并</t>
+    <t>优化投诉处理流程，完善数据库及接口文档，整理项目结构，删除冗余代码，完成项目联调与代码整合</t>
   </si>
   <si>
     <t>吴兴强</t>

--- a/00_团队成员任务记录表.xlsx
+++ b/00_团队成员任务记录表.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>7月4号</t>
   </si>
@@ -26,6 +26,18 @@
   </si>
   <si>
     <t>胡林康</t>
+  </si>
+  <si>
+    <t>项目初始化</t>
+  </si>
+  <si>
+    <t>项目文档编写</t>
+  </si>
+  <si>
+    <t>项目文档编写与测试</t>
+  </si>
+  <si>
+    <t>项目文档编写与PPT制作</t>
   </si>
   <si>
     <t>高攀</t>
@@ -486,80 +498,89 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2">
-        <v>111</v>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/00_团队成员任务记录表.xlsx
+++ b/00_团队成员任务记录表.xlsx
@@ -34,13 +34,13 @@
     <t>数据库设计与实体类创建</t>
   </si>
   <si>
-    <t>Building和Community两个数据表的后端代码编写</t>
-  </si>
-  <si>
-    <t>repair和repair_order两个数据表的后端代码编写</t>
-  </si>
-  <si>
-    <t>inspection和inspection_record两个数据表的后端代码编写</t>
+    <t>楼栋和小区管理模块的后端代码任务逻辑编写</t>
+  </si>
+  <si>
+    <t>保修管理模块的后端代码任务逻辑编写</t>
+  </si>
+  <si>
+    <t>巡检管理模块的后端代码任务逻辑编写</t>
   </si>
   <si>
     <t>李军霖</t>
